--- a/packages/competence/docs/templates/employee-import-template.xlsx
+++ b/packages/competence/docs/templates/employee-import-template.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q32"/>
+  <dimension ref="B2:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -615,6 +615,13 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="39" customHeight="1">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>5. work_site takes a site code, not a name - the valid codes for this deployment are listed under Administration &gt; Work Sites. A code typed with a Cyrillic look-alike letter (e.g. 'О' instead of 'O') is rejected; the import message names the exact character that is wrong.</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -695,7 +702,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>On a re-import, leaving birth_date, gender or starting_date empty keeps whatever is already stored rather than erasing it. To clear one of those, use the Employee Management screen in the application.</t>
+          <t>On a re-import, leaving birth_date, gender, starting_date, work_site or position_name empty keeps whatever is already stored rather than erasing it. To clear one of those, use the Employee Management screen in the application.</t>
         </is>
       </c>
     </row>
@@ -787,6 +794,16 @@
       <c r="Q30" s="6" t="inlineStr">
         <is>
           <t>starting_date</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>work_site</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>position_name</t>
         </is>
       </c>
     </row>
@@ -882,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O401"/>
+  <dimension ref="A1:Q401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -900,6 +917,8 @@
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -976,6 +995,16 @@
       <c r="O1" s="10" t="inlineStr">
         <is>
           <t>starting_date</t>
+        </is>
+      </c>
+      <c r="P1" s="10" t="inlineStr">
+        <is>
+          <t>work_site</t>
+        </is>
+      </c>
+      <c r="Q1" s="10" t="inlineStr">
+        <is>
+          <t>position_name</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7819,7 @@
       <formula>AND(LEN(B2)&gt;0,COUNTIF($B$2:$B$401,B2)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="E2:E401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a permitted value" error="Pick a value from the list. The importer rejects anything else - it will not guess." promptTitle="work_mode" prompt="Permitted: Full-time, Part-time, Contract" type="list">
       <formula1>"Full-time,Part-time,Contract"</formula1>
     </dataValidation>
@@ -7808,6 +7837,9 @@
     </dataValidation>
     <dataValidation sqref="J2:J401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a permitted value" error="Pick a value from the list. The importer rejects anything else - it will not guess." promptTitle="stage" prompt="Permitted: 1, 2, 3" type="list">
       <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a permitted value" error="Pick a value from the list. The importer rejects anything else - it will not guess." promptTitle="gender" prompt="Permitted: M, F" type="list">
+      <formula1>"M,F"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
